--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="536">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedCondition</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedCondition</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:21:37+00:00</t>
+    <t>2025-03-11T16:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ELGA</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ELGA (https://www.elga.gv.at/)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -1256,7 +1256,7 @@
     <t>ICD10</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/bmg-icd-10-2024</t>
+    <t>https://elga.moped.at/ValueSet/ICD10AT</t>
   </si>
   <si>
     <t>Condition.code.coding:ICD10.id</t>
@@ -1277,6 +1277,9 @@
     <t>Condition.code.coding.system</t>
   </si>
   <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/icd-10-bmsgpk-2025</t>
+  </si>
+  <si>
     <t>Condition.code.coding:ICD10.version</t>
   </si>
   <si>
@@ -1307,7 +1310,7 @@
     <t>HDG</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-LKFHauptdiagnosegruppen-valueset</t>
+    <t>https://elga.moped.at/ValueSet/LKFHauptdiagnosegruppen</t>
   </si>
   <si>
     <t>Condition.code.coding:HDG.id</t>
@@ -1319,7 +1322,7 @@
     <t>Condition.code.coding:HDG.system</t>
   </si>
   <si>
-    <t>http://tbd.at/MOPED-LKFHauptdiagnosegruppen</t>
+    <t>https://elga.moped.at/CodeSystem/LKFHauptdiagnosegruppenCS</t>
   </si>
   <si>
     <t>Condition.code.coding:HDG.version</t>
@@ -1396,7 +1399,7 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedEncounter)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedEncounter)
 </t>
   </si>
   <si>
@@ -2028,7 +2031,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.23828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.18359375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -8066,7 +8069,7 @@
         <v>20</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>20</v>
@@ -8137,10 +8140,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8254,10 +8257,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8371,10 +8374,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8488,10 +8491,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8607,13 +8610,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>392</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>20</v>
@@ -8676,7 +8679,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8726,7 +8729,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>399</v>
@@ -8841,7 +8844,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>401</v>
@@ -8958,7 +8961,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>403</v>
@@ -9006,7 +9009,7 @@
         <v>20</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>20</v>
@@ -9077,10 +9080,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9194,10 +9197,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9311,10 +9314,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9428,10 +9431,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9547,10 +9550,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9666,10 +9669,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9695,13 +9698,13 @@
         <v>186</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9730,10 +9733,10 @@
         <v>382</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -9751,7 +9754,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9769,28 +9772,28 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9809,17 +9812,17 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9868,7 +9871,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>89</v>
@@ -9883,16 +9886,16 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -9900,10 +9903,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9926,16 +9929,16 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9985,7 +9988,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10000,16 +10003,16 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10017,10 +10020,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10043,16 +10046,16 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10102,7 +10105,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10117,16 +10120,16 @@
         <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10134,10 +10137,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10160,16 +10163,16 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10219,7 +10222,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10228,13 +10231,13 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>20</v>
@@ -10243,7 +10246,7 @@
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10251,10 +10254,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10277,16 +10280,16 @@
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10336,7 +10339,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10351,16 +10354,16 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10368,10 +10371,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10394,13 +10397,13 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10451,7 +10454,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10475,7 +10478,7 @@
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -10483,10 +10486,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10598,10 +10601,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10715,14 +10718,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10744,10 +10747,10 @@
         <v>137</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>140</v>
@@ -10802,7 +10805,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10834,10 +10837,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10863,10 +10866,10 @@
         <v>186</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10893,11 +10896,11 @@
         <v>20</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -10915,7 +10918,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10939,7 +10942,7 @@
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -10947,10 +10950,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10973,13 +10976,13 @@
         <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11030,7 +11033,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>89</v>
@@ -11045,7 +11048,7 @@
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>20</v>
@@ -11054,7 +11057,7 @@
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -11062,10 +11065,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11088,13 +11091,13 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11145,7 +11148,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11157,7 +11160,7 @@
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
@@ -11169,7 +11172,7 @@
         <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11177,10 +11180,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11292,10 +11295,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11409,14 +11412,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11438,10 +11441,10 @@
         <v>137</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>140</v>
@@ -11496,7 +11499,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11528,10 +11531,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11557,10 +11560,10 @@
         <v>186</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11590,10 +11593,10 @@
         <v>382</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -11611,7 +11614,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11620,7 +11623,7 @@
         <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>101</v>
@@ -11629,7 +11632,7 @@
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>313</v>
@@ -11643,10 +11646,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11669,13 +11672,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11726,7 +11729,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11735,7 +11738,7 @@
         <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>101</v>
@@ -11750,7 +11753,7 @@
         <v>20</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -11758,10 +11761,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11787,10 +11790,10 @@
         <v>186</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11820,10 +11823,10 @@
         <v>382</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
@@ -11841,7 +11844,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11865,7 +11868,7 @@
         <v>20</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -11873,10 +11876,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11899,16 +11902,16 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11938,7 +11941,7 @@
       </c>
       <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>20</v>
@@ -11956,7 +11959,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11980,7 +11983,7 @@
         <v>20</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -11988,10 +11991,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12014,13 +12017,13 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12071,7 +12074,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12092,10 +12095,10 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -881,7 +881,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedPatient)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedBasisPatientvbPK|https://elga.moped.at/StructureDefinition/MopedBasisPatientKlarname)
 </t>
   </si>
   <si>
@@ -1433,7 +1433,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="118.0859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedCondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
